--- a/CS_Schedule.xlsx
+++ b/CS_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tri.cs10\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{270A28B3-4A60-49D3-AE03-3562F14E9F99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{B0B657A1-8751-48FC-98FD-A1B8B642640F}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{270A28B3-4A60-49D3-AE03-3562F14E9F99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{0D56D319-7F80-48D7-825B-70D48D03869A}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="OIkuOF3eHzySP9daFtHtKED1Vs42iBTjzK5rgrBgDMn3Q8tBPUhN7sXGp8zxEqSnFWZeMorQsU25PVQaZjetrg==" workbookSaltValue="qm0JFPilva56DyfEUFRFLQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="284" xr2:uid="{50DCB852-9937-44E1-9912-3F6C24360B60}"/>
@@ -2220,9 +2220,6 @@
       <c r="E10" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="G10" s="23" t="s">
         <v>11</v>
       </c>
@@ -2236,6 +2233,9 @@
         <v>11</v>
       </c>
       <c r="K10" s="21"/>
+      <c r="L10" s="6" t="s">
+        <v>7</v>
+      </c>
       <c r="M10" s="12" t="s">
         <v>11</v>
       </c>

--- a/CS_Schedule.xlsx
+++ b/CS_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tri.cs10\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{270A28B3-4A60-49D3-AE03-3562F14E9F99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{0D56D319-7F80-48D7-825B-70D48D03869A}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="14_{6E0EE5FE-9859-49B9-89AB-A4787C5884FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{7600C441-D680-4040-9A5E-25012F14E4C8}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="OIkuOF3eHzySP9daFtHtKED1Vs42iBTjzK5rgrBgDMn3Q8tBPUhN7sXGp8zxEqSnFWZeMorQsU25PVQaZjetrg==" workbookSaltValue="qm0JFPilva56DyfEUFRFLQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="284" xr2:uid="{50DCB852-9937-44E1-9912-3F6C24360B60}"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
   <si>
     <t>Saturday</t>
   </si>
@@ -797,6 +797,9 @@
     <t>Need Cover</t>
   </si>
   <si>
+    <t>Add OFF</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Ahmed Yasser
 </t>
@@ -831,6 +834,60 @@
         <family val="2"/>
       </rPr>
       <t>01159586006</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4 PM - 1 AM
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>Niight</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>REH</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Tahoma"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
     </r>
   </si>
 </sst>
@@ -1019,7 +1076,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1079,6 +1136,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -1314,7 +1377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1434,6 +1497,18 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1958,8 +2033,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="2" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="33"/>
-      <c r="B1" s="33"/>
+      <c r="A1" s="36"/>
+      <c r="B1" s="36"/>
       <c r="C1" s="27"/>
       <c r="D1" s="5"/>
       <c r="E1" s="27"/>
@@ -1999,33 +2074,33 @@
       <c r="K2" s="21"/>
     </row>
     <row r="3" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="35"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="20">
+        <v>46312</v>
+      </c>
+      <c r="D3" s="20">
+        <v>46313</v>
+      </c>
+      <c r="E3" s="20">
+        <v>46314</v>
+      </c>
+      <c r="F3" s="20">
+        <v>46315</v>
+      </c>
+      <c r="G3" s="20">
+        <v>46316</v>
+      </c>
+      <c r="H3" s="20">
+        <v>46317</v>
+      </c>
+      <c r="I3" s="20">
+        <v>46318</v>
+      </c>
+      <c r="J3" s="20">
         <v>46319</v>
-      </c>
-      <c r="D3" s="20">
-        <v>46320</v>
-      </c>
-      <c r="E3" s="20">
-        <v>46321</v>
-      </c>
-      <c r="F3" s="20">
-        <v>46322</v>
-      </c>
-      <c r="G3" s="20">
-        <v>46323</v>
-      </c>
-      <c r="H3" s="20">
-        <v>46324</v>
-      </c>
-      <c r="I3" s="20">
-        <v>46325</v>
-      </c>
-      <c r="J3" s="20">
-        <v>46326</v>
       </c>
       <c r="K3" s="21"/>
     </row>
@@ -2044,7 +2119,7 @@
       <c r="J4" s="10"/>
       <c r="K4" s="21"/>
     </row>
-    <row r="5" spans="1:13" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="60.75" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>10349</v>
       </c>
@@ -2053,6 +2128,18 @@
       </c>
       <c r="C5" s="6" t="s">
         <v>7</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="23" t="s">
+        <v>26</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>7</v>
@@ -2108,11 +2195,8 @@
       <c r="B7" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>10</v>
+      <c r="D7" s="31" t="s">
+        <v>24</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>10</v>
@@ -2144,11 +2228,14 @@
       <c r="B8" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>10</v>
+      <c r="C8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>12</v>
@@ -2177,14 +2264,14 @@
       <c r="B9" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>12</v>
+      <c r="C9" s="23" t="s">
+        <v>10</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>12</v>
+      <c r="E9" s="23" t="s">
+        <v>11</v>
       </c>
       <c r="F9" s="23" t="s">
         <v>11</v>
@@ -2209,20 +2296,13 @@
     <row r="10" spans="1:13" ht="66.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
       <c r="B10" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>11</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="23" t="s">
         <v>11</v>
       </c>
@@ -2233,19 +2313,16 @@
         <v>11</v>
       </c>
       <c r="K10" s="21"/>
-      <c r="L10" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="M10" s="12" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="str">
+      <c r="A11" s="34" t="str">
         <f>"H.C:      " &amp; COUNTA(B6:B9)</f>
         <v>H.C:      4</v>
       </c>
-      <c r="B11" s="32"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="22" t="str">
         <f t="shared" ref="C11:J11" si="0">IF(
 SUMPRODUCT(--ISNUMBER(SEARCH("TRI",C5:C10)))=0,"",
@@ -2288,97 +2365,57 @@
 SUMPRODUCT(--ISNUMBER(SEARCH("REH",C5:C10))*--ISNUMBER(SEARCH("Training",C5:C10)))&gt;0,
 "- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",C5:C10))*--ISNUMBER(SEARCH("Training",C5:C10)))&amp;" T","")
 )</f>
-        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
+        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M </v>
       </c>
       <c r="D11" s="22" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
       </c>
       <c r="E11" s="22" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 2 M - 1 N </v>
+      </c>
+      <c r="F11" s="22" t="str">
         <f>IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",E6:E10)))=0,"",
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10)))=0,"",
 "TRI : "&amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",E6:E10))*--ISNUMBER(SEARCH("Morning",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",E6:E10))*--ISNUMBER(SEARCH("Morning",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&amp;" M ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",E6:E10))*--ISNUMBER(SEARCH("Between",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",E6:E10))*--ISNUMBER(SEARCH("Between",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&amp;" B ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",E6:E10))*--ISNUMBER(SEARCH("Night",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",E6:E10))*--ISNUMBER(SEARCH("Night",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&amp;" N ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",E6:E10))*--ISNUMBER(SEARCH("Training",E6:E10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",E6:E10))*--ISNUMBER(SEARCH("Training",E6:E10)))&amp;" T","")
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Morning",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Morning",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" M ","")&amp;
+IF(
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Between",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Between",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" B ","")&amp;
+IF(
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Night",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Night",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" N ","")&amp;
+IF(
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Training",F6:F10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Training",F6:F10)))&amp;" T","")
 )
 &amp;
 IF(
 AND(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",E6:E10)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",E6:E10)))&gt;0
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10)))&gt;0,
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10)))&gt;0
 ),
 "   |   ",""
 )
 &amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",E6:E10)))=0,"",
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10)))=0,"",
 "REH : "&amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",E6:E10))*--ISNUMBER(SEARCH("Morning",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",E6:E10))*--ISNUMBER(SEARCH("Morning",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&amp;" M ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",E6:E10))*--ISNUMBER(SEARCH("Between",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",E6:E10))*--ISNUMBER(SEARCH("Between",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&amp;" B ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",E6:E10))*--ISNUMBER(SEARCH("Night",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",E6:E10))*--ISNUMBER(SEARCH("Night",E6:E10))*--ISERROR(SEARCH("Training",E6:E10)))&amp;" N ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",E6:E10))*--ISNUMBER(SEARCH("Training",E6:E10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",E6:E10))*--ISNUMBER(SEARCH("Training",E6:E10)))&amp;" T","")
-)</f>
-        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 2 M - 1 N </v>
-      </c>
-      <c r="F11" s="22" t="str">
-        <f>IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F5:F9)))=0,"",
-"TRI : "&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F5:F9))*--ISNUMBER(SEARCH("Morning",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F5:F9))*--ISNUMBER(SEARCH("Morning",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&amp;" M ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F5:F9))*--ISNUMBER(SEARCH("Between",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F5:F9))*--ISNUMBER(SEARCH("Between",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&amp;" B ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F5:F9))*--ISNUMBER(SEARCH("Night",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F5:F9))*--ISNUMBER(SEARCH("Night",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&amp;" N ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F5:F9))*--ISNUMBER(SEARCH("Training",F5:F9)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F5:F9))*--ISNUMBER(SEARCH("Training",F5:F9)))&amp;" T","")
-)
-&amp;
-IF(
-AND(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F5:F9)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F5:F9)))&gt;0
-),
-"   |   ",""
-)
-&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F5:F9)))=0,"",
-"REH : "&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F5:F9))*--ISNUMBER(SEARCH("Morning",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F5:F9))*--ISNUMBER(SEARCH("Morning",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&amp;" M ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F5:F9))*--ISNUMBER(SEARCH("Between",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",F5:F9))*--ISNUMBER(SEARCH("Between",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&amp;" B ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F5:F9))*--ISNUMBER(SEARCH("Night",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",F5:F9))*--ISNUMBER(SEARCH("Night",F5:F9))*--ISERROR(SEARCH("Training",F5:F9)))&amp;" N ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F5:F9))*--ISNUMBER(SEARCH("Training",F5:F9)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",F5:F9))*--ISNUMBER(SEARCH("Training",F5:F9)))&amp;" T","")
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Morning",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Morning",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" M ","")&amp;
+IF(
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Between",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Between",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" B ","")&amp;
+IF(
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Night",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Night",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" N ","")&amp;
+IF(
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Training",F6:F10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Training",F6:F10)))&amp;" T","")
 )</f>
         <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
       </c>

--- a/CS_Schedule.xlsx
+++ b/CS_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tri.cs10\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="14_{6E0EE5FE-9859-49B9-89AB-A4787C5884FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{7600C441-D680-4040-9A5E-25012F14E4C8}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="14_{6E0EE5FE-9859-49B9-89AB-A4787C5884FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{A453EDFA-5556-4847-B6F0-07FB10897D48}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="OIkuOF3eHzySP9daFtHtKED1Vs42iBTjzK5rgrBgDMn3Q8tBPUhN7sXGp8zxEqSnFWZeMorQsU25PVQaZjetrg==" workbookSaltValue="qm0JFPilva56DyfEUFRFLQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="284" xr2:uid="{50DCB852-9937-44E1-9912-3F6C24360B60}"/>
@@ -29,8 +29,93 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Moamen Bahaa</author>
+  </authors>
+  <commentList>
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{1F6F4024-B2F3-45FA-A834-5F54B1166AB3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Moamen Bahaa:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+بدل اجازه الجمعه 23-10
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{67374EFE-5983-4048-930A-E21AC02CE124}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Moamen Bahaa:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+بدل اجازه السبت 24-10
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{C2593673-D68D-4235-96F9-DF0013934559}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Moamen Bahaa:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+بدل اجازه الجمعه 30-10
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="25">
   <si>
     <t>Saturday</t>
   </si>
@@ -797,98 +882,7 @@
     <t>Need Cover</t>
   </si>
   <si>
-    <t>Add OFF</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ahmed Yasser
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Agency FB"/>
-        <family val="2"/>
-      </rPr>
-      <t>CS Coordinator</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="Agency FB"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Agency FB"/>
-        <family val="2"/>
-      </rPr>
-      <t>01159586006</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">4 PM - 1 AM
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t>Niight</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t>REH</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Tahoma"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
+    <t>---------</t>
   </si>
 </sst>
 </file>
@@ -898,7 +892,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1075,8 +1069,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1136,12 +1143,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -1377,17 +1378,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection hidden="1"/>
     </xf>
@@ -1467,48 +1464,44 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="49" fontId="4" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0" hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1560,7 +1553,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right/>
         <top style="thick">
@@ -2018,7 +2011,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF1824F-A631-434B-B9FC-C592FE1EBC87}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF1824F-A631-434B-B9FC-C592FE1EBC87}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
@@ -2032,298 +2025,295 @@
     <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36"/>
-      <c r="B1" s="36"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="27"/>
+    <row r="1" spans="1:13" s="26" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="23"/>
     </row>
     <row r="2" spans="1:13" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="13" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="21"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="20">
-        <v>46312</v>
-      </c>
-      <c r="D3" s="20">
-        <v>46313</v>
-      </c>
-      <c r="E3" s="20">
-        <v>46314</v>
-      </c>
-      <c r="F3" s="20">
-        <v>46315</v>
-      </c>
-      <c r="G3" s="20">
-        <v>46316</v>
-      </c>
-      <c r="H3" s="20">
-        <v>46317</v>
-      </c>
-      <c r="I3" s="20">
-        <v>46318</v>
-      </c>
-      <c r="J3" s="20">
+      <c r="B3" s="36"/>
+      <c r="C3" s="19">
         <v>46319</v>
       </c>
-      <c r="K3" s="21"/>
+      <c r="D3" s="19">
+        <v>46320</v>
+      </c>
+      <c r="E3" s="19">
+        <v>46321</v>
+      </c>
+      <c r="F3" s="19">
+        <v>46322</v>
+      </c>
+      <c r="G3" s="19">
+        <v>46323</v>
+      </c>
+      <c r="H3" s="19">
+        <v>46324</v>
+      </c>
+      <c r="I3" s="19">
+        <v>46325</v>
+      </c>
+      <c r="J3" s="19">
+        <v>46326</v>
+      </c>
+      <c r="K3" s="20"/>
     </row>
     <row r="4" spans="1:13" ht="10.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="21"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="20"/>
     </row>
     <row r="5" spans="1:13" ht="60.75" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="18">
+      <c r="A5" s="17">
         <v>10349</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="E5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="I5" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" s="21"/>
-      <c r="M5" s="7" t="s">
+      <c r="K5" s="20"/>
+      <c r="M5" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+      <c r="A6" s="17">
         <v>10381</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="21"/>
-      <c r="M6" s="7" t="s">
+      <c r="K6" s="20"/>
+      <c r="M6" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18">
+      <c r="A7" s="17">
         <v>10542</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="C7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="E7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="F7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="G7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="6" t="s">
+      <c r="H7" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="J7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="21"/>
-      <c r="M7" s="7" t="s">
+      <c r="K7" s="20"/>
+      <c r="M7" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="19">
+      <c r="A8" s="18">
         <v>10827</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="F8" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="K8" s="21"/>
-      <c r="M8" s="12" t="s">
+      <c r="K8" s="20"/>
+      <c r="M8" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="19">
+      <c r="A9" s="18">
         <v>10868</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="D9" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="21"/>
-      <c r="M9" s="12" t="s">
+      <c r="K9" s="20"/>
+      <c r="M9" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="66.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19"/>
-      <c r="B10" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="K10" s="21"/>
-      <c r="M10" s="12" t="s">
+    <row r="10" spans="1:13" ht="41.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="K10" s="20"/>
+      <c r="M10" s="11" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="str">
+      <c r="A11" s="32" t="str">
         <f>"H.C:      " &amp; COUNTA(B6:B9)</f>
         <v>H.C:      4</v>
       </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="22" t="str">
+      <c r="B11" s="33"/>
+      <c r="C11" s="21" t="str">
         <f t="shared" ref="C11:J11" si="0">IF(
 SUMPRODUCT(--ISNUMBER(SEARCH("TRI",C5:C10)))=0,"",
 "TRI : "&amp;
@@ -2365,77 +2355,37 @@
 SUMPRODUCT(--ISNUMBER(SEARCH("REH",C5:C10))*--ISNUMBER(SEARCH("Training",C5:C10)))&gt;0,
 "- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",C5:C10))*--ISNUMBER(SEARCH("Training",C5:C10)))&amp;" T","")
 )</f>
-        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M </v>
-      </c>
-      <c r="D11" s="22" t="str">
+        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
+      </c>
+      <c r="D11" s="21" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
       </c>
-      <c r="E11" s="22" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 2 M - 1 N </v>
-      </c>
-      <c r="F11" s="22" t="str">
-        <f>IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10)))=0,"",
-"TRI : "&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Morning",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Morning",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" M ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Between",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Between",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" B ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Night",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Night",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" N ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Training",F6:F10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10))*--ISNUMBER(SEARCH("Training",F6:F10)))&amp;" T","")
-)
-&amp;
-IF(
-AND(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",F6:F10)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10)))&gt;0
-),
-"   |   ",""
-)
-&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10)))=0,"",
-"REH : "&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Morning",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Morning",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" M ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Between",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Between",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" B ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Night",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Night",F6:F10))*--ISERROR(SEARCH("Training",F6:F10)))&amp;" N ","")&amp;
-IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Training",F6:F10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",F6:F10))*--ISNUMBER(SEARCH("Training",F6:F10)))&amp;" T","")
-)</f>
-        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
-      </c>
-      <c r="G11" s="22" t="str">
+      <c r="E11" s="21" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
       </c>
-      <c r="H11" s="22" t="str">
+      <c r="F11" s="21" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
       </c>
-      <c r="I11" s="22" t="str">
+      <c r="G11" s="21" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
       </c>
-      <c r="J11" s="22" t="str">
+      <c r="H11" s="21" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
       </c>
-      <c r="K11" s="22" t="str">
+      <c r="I11" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
+      </c>
+      <c r="J11" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
+      </c>
+      <c r="K11" s="21" t="str">
         <f>IF(
 SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10)))=0,"",
 "TRI : "&amp;
@@ -2481,12 +2431,12 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="26" t="s">
+      <c r="B12" s="22" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0v2Iz3PJsXbuA2AWUATMWiixQYyOPPdTuLX7p943Cc0b3l1xy+vG2GF0QVCog7Dj0Bf4DUEoy6rBhVxDMoIWAQ==" saltValue="akqL41CpbKGaIAFoDCOicw==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
   <autoFilter ref="B3:B12" xr:uid="{84F938A2-05CE-4D72-8E8F-C4661814570E}"/>
   <mergeCells count="3">
     <mergeCell ref="A11:B11"/>
@@ -2497,8 +2447,9 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2512,32 +2463,32 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:1" ht="39.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="39.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="39.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="39.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="39.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="39.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>13</v>
       </c>
     </row>

--- a/CS_Schedule.xlsx
+++ b/CS_Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tri.cs10\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="14_{6E0EE5FE-9859-49B9-89AB-A4787C5884FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{A453EDFA-5556-4847-B6F0-07FB10897D48}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="113_{1792430D-00C1-4DE2-99B0-00068BC4FB37}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{27499DC5-351E-4B5B-84EE-9A6112E8AA40}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="OIkuOF3eHzySP9daFtHtKED1Vs42iBTjzK5rgrBgDMn3Q8tBPUhN7sXGp8zxEqSnFWZeMorQsU25PVQaZjetrg==" workbookSaltValue="qm0JFPilva56DyfEUFRFLQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="284" xr2:uid="{50DCB852-9937-44E1-9912-3F6C24360B60}"/>
@@ -35,7 +35,7 @@
     <author>Moamen Bahaa</author>
   </authors>
   <commentList>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{1F6F4024-B2F3-45FA-A834-5F54B1166AB3}">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{1F6F4024-B2F3-45FA-A834-5F54B1166AB3}">
       <text>
         <r>
           <rPr>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{67374EFE-5983-4048-930A-E21AC02CE124}">
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{67374EFE-5983-4048-930A-E21AC02CE124}">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{C2593673-D68D-4235-96F9-DF0013934559}">
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{C2593673-D68D-4235-96F9-DF0013934559}">
       <text>
         <r>
           <rPr>
@@ -110,12 +110,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{F8D48302-D9DB-47C0-AE94-9B26AC7919E2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Moamen Bahaa:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+بدل اجازه الجمعه 23-10
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="25">
   <si>
     <t>Saturday</t>
   </si>
@@ -1378,7 +1403,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1504,24 +1529,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -2013,106 +2050,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAF1824F-A631-434B-B9FC-C592FE1EBC87}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.5703125" style="1" customWidth="1"/>
-    <col min="3" max="10" width="23" style="1" customWidth="1"/>
-    <col min="11" max="11" width="2" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="30.140625" style="1" hidden="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="3" max="3" width="23.140625" style="1" customWidth="1"/>
+    <col min="4" max="11" width="23" style="1" customWidth="1"/>
+    <col min="12" max="12" width="2" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="26" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34"/>
-      <c r="B1" s="34"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="4"/>
+    <row r="1" spans="1:14" s="26" customFormat="1" ht="4.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="35"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="23"/>
       <c r="I1" s="4"/>
-      <c r="J1" s="23"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="23"/>
     </row>
-    <row r="2" spans="1:13" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="14.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="I2" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="J2" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="K2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
     </row>
-    <row r="3" spans="1:13" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="35" t="s">
+    <row r="3" spans="1:14" ht="16.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
       <c r="C3" s="19">
+        <v>46318</v>
+      </c>
+      <c r="D3" s="19">
         <v>46319</v>
       </c>
-      <c r="D3" s="19">
+      <c r="E3" s="19">
         <v>46320</v>
       </c>
-      <c r="E3" s="19">
+      <c r="F3" s="19">
         <v>46321</v>
       </c>
-      <c r="F3" s="19">
+      <c r="G3" s="19">
         <v>46322</v>
       </c>
-      <c r="G3" s="19">
+      <c r="H3" s="19">
         <v>46323</v>
       </c>
-      <c r="H3" s="19">
+      <c r="I3" s="19">
         <v>46324</v>
       </c>
-      <c r="I3" s="19">
+      <c r="J3" s="19">
         <v>46325</v>
       </c>
-      <c r="J3" s="19">
+      <c r="K3" s="19">
         <v>46326</v>
       </c>
-      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
     </row>
-    <row r="4" spans="1:13" ht="10.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" ht="10.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="8"/>
-      <c r="C4" s="9"/>
+      <c r="C4" s="38"/>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="20"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="20"/>
     </row>
-    <row r="5" spans="1:13" ht="60.75" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" ht="60.75" hidden="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="17">
         <v>10349</v>
       </c>
@@ -2122,41 +2168,44 @@
       <c r="C5" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>7</v>
+      <c r="D5" s="28" t="s">
+        <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="I5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="J5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="28" t="s">
+      <c r="K5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="M5" s="6" t="s">
+      <c r="L5" s="20"/>
+      <c r="N5" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17">
         <v>10381</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>9</v>
+      <c r="C6" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="D6" s="29" t="s">
         <v>9</v>
@@ -2170,32 +2219,35 @@
       <c r="G6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="K6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="20"/>
-      <c r="M6" s="6" t="s">
+      <c r="L6" s="20"/>
+      <c r="N6" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="17">
         <v>10542</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>10</v>
       </c>
       <c r="E7" s="28" t="s">
         <v>10</v>
@@ -2207,34 +2259,37 @@
         <v>10</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I7" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="K7" s="20"/>
-      <c r="M7" s="6" t="s">
+      <c r="L7" s="20"/>
+      <c r="N7" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="18">
         <v>10827</v>
       </c>
       <c r="B8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="31" t="s">
+      <c r="E8" s="31" t="s">
         <v>11</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>12</v>
       </c>
       <c r="F8" s="29" t="s">
         <v>12</v>
@@ -2242,21 +2297,24 @@
       <c r="G8" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="J8" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="J8" s="28" t="s">
+      <c r="K8" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="20"/>
-      <c r="M8" s="11" t="s">
+      <c r="L8" s="20"/>
+      <c r="N8" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="60.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="18">
         <v>10868</v>
       </c>
@@ -2269,17 +2327,17 @@
       <c r="D9" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="H9" s="28" t="s">
         <v>11</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>12</v>
       </c>
       <c r="I9" s="29" t="s">
         <v>12</v>
@@ -2287,34 +2345,38 @@
       <c r="J9" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="20"/>
-      <c r="M9" s="11" t="s">
+      <c r="K9" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="20"/>
+      <c r="N9" s="11" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="41.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="41.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18"/>
       <c r="B10" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="29"/>
+      <c r="C10" s="39"/>
       <c r="D10" s="29"/>
       <c r="E10" s="29"/>
       <c r="F10" s="29"/>
       <c r="G10" s="29"/>
-      <c r="K10" s="20"/>
-      <c r="M10" s="11" t="s">
+      <c r="H10" s="29"/>
+      <c r="L10" s="20"/>
+      <c r="N10" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="32" t="str">
+    <row r="11" spans="1:14" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="33" t="str">
         <f>"H.C:      " &amp; COUNTA(B6:B9)</f>
         <v>H.C:      4</v>
       </c>
-      <c r="B11" s="33"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="21" t="str">
-        <f t="shared" ref="C11:J11" si="0">IF(
+        <f t="shared" ref="C11:K11" si="0">IF(
 SUMPRODUCT(--ISNUMBER(SEARCH("TRI",C5:C10)))=0,"",
 "TRI : "&amp;
 IF(
@@ -2386,57 +2448,62 @@
         <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
       </c>
       <c r="K11" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">TRI : 1 M - 1 N    |   REH : 1 M - 1 N </v>
+      </c>
+      <c r="L11" s="21" t="str">
         <f>IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10)))=0,"",
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",L5:L10)))=0,"",
 "TRI : "&amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10))*--ISNUMBER(SEARCH("Morning",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10))*--ISNUMBER(SEARCH("Morning",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&amp;" M ","")&amp;
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",L5:L10))*--ISNUMBER(SEARCH("Morning",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&gt;0,
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",L5:L10))*--ISNUMBER(SEARCH("Morning",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&amp;" M ","")&amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10))*--ISNUMBER(SEARCH("Between",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10))*--ISNUMBER(SEARCH("Between",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&amp;" B ","")&amp;
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",L5:L10))*--ISNUMBER(SEARCH("Between",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",L5:L10))*--ISNUMBER(SEARCH("Between",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&amp;" B ","")&amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10))*--ISNUMBER(SEARCH("Night",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10))*--ISNUMBER(SEARCH("Night",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&amp;" N ","")&amp;
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",L5:L10))*--ISNUMBER(SEARCH("Night",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",L5:L10))*--ISNUMBER(SEARCH("Night",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&amp;" N ","")&amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10))*--ISNUMBER(SEARCH("Training",K5:K10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10))*--ISNUMBER(SEARCH("Training",K5:K10)))&amp;" T","")
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",L5:L10))*--ISNUMBER(SEARCH("Training",L5:L10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("TRI",L5:L10))*--ISNUMBER(SEARCH("Training",L5:L10)))&amp;" T","")
 )
 &amp;
 IF(
 AND(
-SUMPRODUCT(--ISNUMBER(SEARCH("TRI",K5:K10)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",K5:K10)))&gt;0
+SUMPRODUCT(--ISNUMBER(SEARCH("TRI",L5:L10)))&gt;0,
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",L5:L10)))&gt;0
 ),
 "   |   ",""
 )
 &amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",K5:K10)))=0,"",
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",L5:L10)))=0,"",
 "REH : "&amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",K5:K10))*--ISNUMBER(SEARCH("Morning",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&gt;0,
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",K5:K10))*--ISNUMBER(SEARCH("Morning",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&amp;" M ","")&amp;
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",L5:L10))*--ISNUMBER(SEARCH("Morning",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&gt;0,
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",L5:L10))*--ISNUMBER(SEARCH("Morning",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&amp;" M ","")&amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",K5:K10))*--ISNUMBER(SEARCH("Between",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",K5:K10))*--ISNUMBER(SEARCH("Between",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&amp;" B ","")&amp;
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",L5:L10))*--ISNUMBER(SEARCH("Between",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",L5:L10))*--ISNUMBER(SEARCH("Between",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&amp;" B ","")&amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",K5:K10))*--ISNUMBER(SEARCH("Night",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",K5:K10))*--ISNUMBER(SEARCH("Night",K5:K10))*--ISERROR(SEARCH("Training",K5:K10)))&amp;" N ","")&amp;
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",L5:L10))*--ISNUMBER(SEARCH("Night",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",L5:L10))*--ISNUMBER(SEARCH("Night",L5:L10))*--ISERROR(SEARCH("Training",L5:L10)))&amp;" N ","")&amp;
 IF(
-SUMPRODUCT(--ISNUMBER(SEARCH("REH",K5:K10))*--ISNUMBER(SEARCH("Training",K5:K10)))&gt;0,
-"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",K5:K10))*--ISNUMBER(SEARCH("Training",K5:K10)))&amp;" T","")
+SUMPRODUCT(--ISNUMBER(SEARCH("REH",L5:L10))*--ISNUMBER(SEARCH("Training",L5:L10)))&gt;0,
+"- "&amp;SUMPRODUCT(--ISNUMBER(SEARCH("REH",L5:L10))*--ISNUMBER(SEARCH("Training",L5:L10)))&amp;" T","")
 )</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B12" s="22" t="s">
         <v>23</v>
       </c>
+      <c r="C12" s="22"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0v2Iz3PJsXbuA2AWUATMWiixQYyOPPdTuLX7p943Cc0b3l1xy+vG2GF0QVCog7Dj0Bf4DUEoy6rBhVxDMoIWAQ==" saltValue="akqL41CpbKGaIAFoDCOicw==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="gHFq8WDvfqvwlQyDgcQxT2ILejYjU2LoL/fYnBoLr9xlNKBnrFze7sB95pXXbrop9zyyJBsA4a+fEE3pKC1KCA==" saltValue="oTMMQtkWkgmMTQOXXE2Ipw==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
   <autoFilter ref="B3:B12" xr:uid="{84F938A2-05CE-4D72-8E8F-C4661814570E}"/>
   <mergeCells count="3">
     <mergeCell ref="A11:B11"/>
